--- a/Employee_Reports_wi48/Arvin Clyde D.Crisme Q0596.xlsx
+++ b/Employee_Reports_wi48/Arvin Clyde D.Crisme Q0596.xlsx
@@ -569,11 +569,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -618,11 +618,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -667,11 +667,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -716,11 +716,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -765,11 +765,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -814,11 +814,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -863,11 +863,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -912,11 +912,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -961,11 +961,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1010,11 +1010,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1059,11 +1059,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1108,11 +1108,11 @@
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1157,11 +1157,11 @@
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1206,11 +1206,11 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1255,11 +1255,11 @@
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1304,11 +1304,11 @@
         </is>
       </c>
       <c r="H18" s="3" t="n">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -1353,11 +1353,11 @@
         </is>
       </c>
       <c r="H19" s="3" t="n">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1402,11 +1402,11 @@
         </is>
       </c>
       <c r="H20" s="3" t="n">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1451,11 +1451,11 @@
         </is>
       </c>
       <c r="H21" s="3" t="n">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -1500,11 +1500,11 @@
         </is>
       </c>
       <c r="H22" s="3" t="n">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
@@ -1549,11 +1549,11 @@
         </is>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-15</v>
+        <v>-18</v>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
@@ -1598,11 +1598,11 @@
         </is>
       </c>
       <c r="H24" s="3" t="n">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
@@ -1635,11 +1635,11 @@
         </is>
       </c>
       <c r="H25" s="3" t="n">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -1672,11 +1672,11 @@
         </is>
       </c>
       <c r="H26" s="3" t="n">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
@@ -1709,11 +1709,11 @@
         </is>
       </c>
       <c r="H27" s="3" t="n">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
